--- a/output/pdf_financials_xlsx/KYS.H.xlsx
+++ b/output/pdf_financials_xlsx/KYS.H.xlsx
@@ -7312,10 +7312,10 @@
         </is>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.110997</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.151444</v>
+        <v>-1.625345</v>
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
@@ -10398,7 +10398,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
